--- a/artfynd/A 21006-2022 artfynd.xlsx
+++ b/artfynd/A 21006-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21006-2022 artfynd.xlsx
+++ b/artfynd/A 21006-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105532464</v>
+        <v>105532463</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>403768.0724845328</v>
+        <v>403863</v>
       </c>
       <c r="R2" t="n">
-        <v>7010991.346770037</v>
+        <v>7011019</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105532463</v>
+        <v>112828407</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bygget, Ottsjö, Jmt</t>
+          <t>blisterflon Ottsjö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>403862.4642022781</v>
+        <v>403881</v>
       </c>
       <c r="R3" t="n">
-        <v>7011019.671710812</v>
+        <v>7011014</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +837,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +862,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112828407</v>
+        <v>112828408</v>
       </c>
       <c r="B4" t="n">
-        <v>56753</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403880</v>
+        <v>403873</v>
       </c>
       <c r="R4" t="n">
-        <v>7011014</v>
+        <v>7011019</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,15 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112828411</v>
+        <v>112828409</v>
       </c>
       <c r="B5" t="n">
-        <v>56753</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>403923</v>
+        <v>403876</v>
       </c>
       <c r="R5" t="n">
-        <v>7011096</v>
+        <v>7011078</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1051,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,12 +1081,7 @@
         <v>112828410</v>
       </c>
       <c r="B6" t="n">
-        <v>56753</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112828409</v>
+        <v>112828411</v>
       </c>
       <c r="B7" t="n">
-        <v>56753</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>403876</v>
+        <v>403923</v>
       </c>
       <c r="R7" t="n">
-        <v>7011078</v>
+        <v>7011095</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1255,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,12 +1285,7 @@
         <v>112828412</v>
       </c>
       <c r="B8" t="n">
-        <v>56753</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>403928</v>
+        <v>403927</v>
       </c>
       <c r="R8" t="n">
-        <v>7011094</v>
+        <v>7011095</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,15 +1384,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112828408</v>
+        <v>112828413</v>
       </c>
       <c r="B9" t="n">
-        <v>56753</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403872</v>
+        <v>403944</v>
       </c>
       <c r="R9" t="n">
-        <v>7011019</v>
+        <v>7011101</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,7 +1459,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,6 +1483,218 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>105532443</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bygget, Ottsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>403872</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7010995</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-10-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-10-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Sjungande och noterad på nära håll.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>78466321</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56689</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bygget, Ottsjö, Ottsjö, Undersåker, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>403689</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7011031</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2019-06-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2019-06-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>märklig päls, angripen av någonting??</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21006-2022 artfynd.xlsx
+++ b/artfynd/A 21006-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105532463</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112828407</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112828408</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112828409</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112828410</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112828411</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112828412</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112828413</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105532443</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1695,8 +1745,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78466321</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>